--- a/src/main/resources/geoEGiBforms/Adresy.xlsx
+++ b/src/main/resources/geoEGiBforms/Adresy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="131">
   <si>
     <t>przedmiotowa</t>
   </si>
@@ -35,267 +35,436 @@
     <t>KERG</t>
   </si>
   <si>
-    <t>Beata Weronika Mieczkowska</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161 obręb: Biała Piska
-162/18 obręb: Biała Piska
-</t>
-  </si>
-  <si>
-    <t>Żeromskiego 2</t>
+    <t>Gmina Biała Piska</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111/23 obręb: Biała Piska
+147/1 obręb: Biała Piska
+147/6 obręb: Biała Piska
+147/10 obręb: Biała Piska
+147/12 obręb: Biała Piska
+147/16 obręb: Biała Piska
+147/19 obręb: Biała Piska
+147/21 obręb: Biała Piska
+147/22 obręb: Biała Piska
+148/1 obręb: Biała Piska
+157 obręb: Biała Piska
+</t>
+  </si>
+  <si>
+    <t>Plac Adama Mickiewicza 25</t>
   </si>
   <si>
     <t>12-230 Biała Piska</t>
   </si>
   <si>
-    <t xml:space="preserve">OL1P/00001948/8
-OL1P/00001948/8
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> G.6642.1.2073.2025</t>
-  </si>
-  <si>
-    <t>Alicja Mieczkowska</t>
-  </si>
-  <si>
-    <t>Żeromskiego 2/2</t>
-  </si>
-  <si>
-    <t>małż. Robert Masłowski i 
-        Luiza Agnieszka Masłowska</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162/12 obręb: Biała Piska
-</t>
-  </si>
-  <si>
-    <t>Żeromskiego 4/1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OL1P/00021535/6
-</t>
-  </si>
-  <si>
-    <t>małż. Zbigniew Falkowski i 
-        Barbara Falkowska</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162/14 obręb: Biała Piska
-</t>
-  </si>
-  <si>
-    <t>Sienkiewicza 5/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OL1P/00024463/1
-</t>
-  </si>
-  <si>
-    <t>Patryk Bartnicki</t>
-  </si>
-  <si>
-    <t>Włosty 13</t>
-  </si>
-  <si>
-    <t>Mikołaj Malinowski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162/16 obręb: Biała Piska
-</t>
-  </si>
-  <si>
-    <t>Kajki 9/13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OL1P/00027671/3
-</t>
-  </si>
-  <si>
-    <t>Agnieszka Piontek-prusinowska</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162/1 obręb: Biała Piska
-</t>
-  </si>
-  <si>
-    <t>Żeromskiego 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OL1P/00012704/6
-</t>
-  </si>
-  <si>
-    <t>Zbigniew Lipiński</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162/20 obręb: Biała Piska
-</t>
-  </si>
-  <si>
-    <t>Sienkiewicza 1/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OL1P/00039553/7
-</t>
-  </si>
-  <si>
-    <t>małż. Stanisław Galanty i 
-        Elżbieta Galanty</t>
-  </si>
-  <si>
-    <t>Zalesie 30/1</t>
-  </si>
-  <si>
-    <t>Ewa Bartosek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162/3 obręb: Biała Piska
-</t>
-  </si>
-  <si>
-    <t>Konopki 3/3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OL1P/00022691/4
-</t>
-  </si>
-  <si>
-    <t>Gmina Biała Piska</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162/3 obręb: Biała Piska
-162/5 obręb: Biała Piska
-162/7 obręb: Biała Piska
-162/9 obręb: Biała Piska
-162/14 obręb: Biała Piska
-162/16 obręb: Biała Piska
-162/19 obręb: Biała Piska
-162/20 obręb: Biała Piska
-162/21 obręb: Biała Piska
-</t>
-  </si>
-  <si>
-    <t>Plac Adama Mickiewicza 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OL1P/00022691/4
-OL1P/00014260/5
-OL1P/00018198/7
+    <t xml:space="preserve">OL1P/00012410/8
+OL1P/00011813/6
+OL1P/00019190/8
 OL1P/00012410/8
-OL1P/00024463/1
-OL1P/00027671/3
 OL1P/00012410/8
-OL1P/00039553/7
+OL1P/00035936/8
 OL1P/00012410/8
-</t>
-  </si>
-  <si>
-    <t>małż. Dariusz Obrycki i 
-        Maria Obrycka</t>
-  </si>
-  <si>
-    <t>Sienkiewicza 3/3</t>
-  </si>
-  <si>
-    <t>Maria Markowska</t>
-  </si>
-  <si>
-    <t>Sienkiewicza 3/2</t>
-  </si>
-  <si>
-    <t>Rafał Bogdański</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162/5 obręb: Biała Piska
-</t>
-  </si>
-  <si>
-    <t>Sienkiewicza 11/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OL1P/00014260/5
-</t>
-  </si>
-  <si>
-    <t>małż. Ryszard Hętnik i 
-        Urszula Hętnik</t>
-  </si>
-  <si>
-    <t>Kumielsk 28/2</t>
-  </si>
-  <si>
-    <t>małż. Mariusz Jacek Długozima i 
-        Agnieszka Długozima</t>
-  </si>
-  <si>
-    <t>Tadeusza Kościuszki 5/2
-Kolonia Kawałek 7</t>
-  </si>
-  <si>
-    <t>12-200 Pisz
-12-230 Biała Piska</t>
-  </si>
-  <si>
-    <t>małż. Karol Chmielewski i 
-        Kinga Barbara Chmielewska</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162/7 obręb: Biała Piska
-</t>
-  </si>
-  <si>
-    <t>Plac Adama Mickiewicza 5/2
-Łodygowo 19/1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OL1P/00018198/7
-</t>
-  </si>
-  <si>
-    <t>małż. Krzysztof Ryży i 
-        Monika Ryży</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164 obręb: Biała Piska
-</t>
-  </si>
-  <si>
-    <t>Żeromskiego 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OL1P/00005165/3
-</t>
-  </si>
-  <si>
-    <t>Województwo Warmińsko-mazurskie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50/2 obręb: Biała Piska
-</t>
-  </si>
-  <si>
-    <t>10-562 Olsztyn</t>
-  </si>
-  <si>
-    <t>Ul.emilii Plater 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OL1P/00026482/4
-</t>
-  </si>
-  <si>
-    <t>Zarząd Dróg Wojewódzkich W Olsztynie</t>
-  </si>
-  <si>
-    <t>10-602 Olsztyn</t>
-  </si>
-  <si>
-    <t>Ul.pstrowskiego 28 B</t>
-  </si>
-  <si>
-    <t>161</t>
+OL1P/00040202/2
+OL1P/00012410/8
+OL1P/00012410/8
+OL1P/00012410/8
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> G.6642.1.2074.2025</t>
+  </si>
+  <si>
+    <t>Powiatowy Zarząd Dróg W Piszu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113 obręb: Biała Piska
+</t>
+  </si>
+  <si>
+    <t>Czerniewskiego 6</t>
+  </si>
+  <si>
+    <t>12-200 Pisz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL1P/00025832/6
+</t>
+  </si>
+  <si>
+    <t>Powiat Piski</t>
+  </si>
+  <si>
+    <t>Warszawska 1</t>
+  </si>
+  <si>
+    <t>małż. Andrzej Sadowski i 
+        Jadwiga Sadowska</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147/13 obręb: Biała Piska
+</t>
+  </si>
+  <si>
+    <t>Moniuszki 2/1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32972
+</t>
+  </si>
+  <si>
+    <t>Alicja Wronkowska</t>
+  </si>
+  <si>
+    <t>Moniuszki 2/2</t>
+  </si>
+  <si>
+    <t>małż. Marcin Niedźwiedzki i 
+        Joanna Niedźwiedzka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147/16 obręb: Biała Piska
+</t>
+  </si>
+  <si>
+    <t>Olsztyńska 44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL1P/00035936/8
+</t>
+  </si>
+  <si>
+    <t>Irena Burlińska</t>
+  </si>
+  <si>
+    <t>Przemysłowa 4/39</t>
+  </si>
+  <si>
+    <t>12-100 Szczytno</t>
+  </si>
+  <si>
+    <t>Robert Zieliński</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147/17 obręb: Biała Piska
+148/2 obręb: Biała Piska
+</t>
+  </si>
+  <si>
+    <t>Witosa 2/16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL1P/00038156/7
+OL1P/00002413/6
+</t>
+  </si>
+  <si>
+    <t>Tomasz Wojsław</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147/1 obręb: Biała Piska
+</t>
+  </si>
+  <si>
+    <t>Kajki 12/1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL1P/00011813/6
+</t>
+  </si>
+  <si>
+    <t>Ignacy Józef Bernekier</t>
+  </si>
+  <si>
+    <t>Witosa 3/13</t>
+  </si>
+  <si>
+    <t>Krystyna Wojsław</t>
+  </si>
+  <si>
+    <t>Targowa 1/7</t>
+  </si>
+  <si>
+    <t>Sylwester Wojsław</t>
+  </si>
+  <si>
+    <t>małż. Wojciech Ławski i 
+        Magdalena Ławska</t>
+  </si>
+  <si>
+    <t>Targowa 1/23</t>
+  </si>
+  <si>
+    <t>małż. Leszek Nawrocki i 
+        Mieczysława Piech</t>
+  </si>
+  <si>
+    <t>Targowa 1/5</t>
+  </si>
+  <si>
+    <t>małż. Wojciech Kamil Rutkowski i 
+        Sylwia Rutkowska</t>
+  </si>
+  <si>
+    <t>Szkody 2b</t>
+  </si>
+  <si>
+    <t>Elżbieta Kowalska</t>
+  </si>
+  <si>
+    <t>Witosa 6/17</t>
+  </si>
+  <si>
+    <t>Beata Ehlert</t>
+  </si>
+  <si>
+    <t>Targowa 1/1</t>
+  </si>
+  <si>
+    <t>Biała Piska</t>
+  </si>
+  <si>
+    <t>Adam Badurek</t>
+  </si>
+  <si>
+    <t>Targowa 1/10</t>
+  </si>
+  <si>
+    <t>małż. Dariusz Wiśniewski i 
+        Sylwia Wiśniewska</t>
+  </si>
+  <si>
+    <t>Targowa 1/21</t>
+  </si>
+  <si>
+    <t>Genowefa Rotkiewicz</t>
+  </si>
+  <si>
+    <t>Targowa 1/18</t>
+  </si>
+  <si>
+    <t>małż. Jan Olszewski i 
+        Helena Olszewska</t>
+  </si>
+  <si>
+    <t>Targowa 1/24</t>
+  </si>
+  <si>
+    <t>Alicja Halina Laszkowska</t>
+  </si>
+  <si>
+    <t>Targowa 1/4</t>
+  </si>
+  <si>
+    <t>Tomasz Bernekier</t>
+  </si>
+  <si>
+    <t>Warmińska 1/28</t>
+  </si>
+  <si>
+    <t>Marek Bernekier</t>
+  </si>
+  <si>
+    <t>Cerkiewnik 69a</t>
+  </si>
+  <si>
+    <t>11-040 Dobre Miasto</t>
+  </si>
+  <si>
+    <t>Lucyna Sokołowska</t>
+  </si>
+  <si>
+    <t>Targowa 1/6</t>
+  </si>
+  <si>
+    <t>małż. Jerzy Abdon Grzyb i 
+        Wiesława Grzyb</t>
+  </si>
+  <si>
+    <t>Targowa 1/20</t>
+  </si>
+  <si>
+    <t>Krzysztof Bernekier</t>
+  </si>
+  <si>
+    <t>10-684 Olsztyn</t>
+  </si>
+  <si>
+    <t>Ul.mieczysława Orłowicza 23 M.5</t>
+  </si>
+  <si>
+    <t>małż. Wacław Markowski i 
+        Danuta Markowska</t>
+  </si>
+  <si>
+    <t>Zabielne 7</t>
+  </si>
+  <si>
+    <t>małż. Jarosław Ciok i 
+        Regina Elżbieta Ciok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147/21 obręb: Biała Piska
+</t>
+  </si>
+  <si>
+    <t>Moniuszki 12/1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL1P/00040202/2
+</t>
+  </si>
+  <si>
+    <t>Arleta Ptaszyńska</t>
+  </si>
+  <si>
+    <t>Moniuszki 12/2</t>
+  </si>
+  <si>
+    <t>małż. Tadeusz Święciński i 
+        Jadwiga Święcińska</t>
+  </si>
+  <si>
+    <t>Moniuszki 12/3</t>
+  </si>
+  <si>
+    <t>Joanna Koszykowska</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147/4 obręb: Biała Piska
+</t>
+  </si>
+  <si>
+    <t>Moniuszki 4/5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL1P/00016819/3
+</t>
+  </si>
+  <si>
+    <t>Irena Bogusława Tereszczak</t>
+  </si>
+  <si>
+    <t>Budziski 5/2</t>
+  </si>
+  <si>
+    <t>18-520 Stawiski</t>
+  </si>
+  <si>
+    <t>małż. Karol Zawacki i 
+        Hanna Edyta Zawacka</t>
+  </si>
+  <si>
+    <t>Moniuszki 4/4</t>
+  </si>
+  <si>
+    <t>małż. Kazimierz Kossakowski i 
+        Kazimiera Kossakowska</t>
+  </si>
+  <si>
+    <t>Moniuszki 4/8</t>
+  </si>
+  <si>
+    <t>Krystyna Janiszewska</t>
+  </si>
+  <si>
+    <t>Aleja Wojska Polskiego 46/4</t>
+  </si>
+  <si>
+    <t>18-300 Zambrów</t>
+  </si>
+  <si>
+    <t>małż. Krzysztof Grenda i 
+        Zofia Grenda</t>
+  </si>
+  <si>
+    <t>Moniuszki 4/3</t>
+  </si>
+  <si>
+    <t>Ewa Dorota Gałązka</t>
+  </si>
+  <si>
+    <t>Sokoły Jeziorne 1/2</t>
+  </si>
+  <si>
+    <t>małż. Paweł Poreda i 
+        Aneta Poreda</t>
+  </si>
+  <si>
+    <t>Moniuszki 4/6</t>
+  </si>
+  <si>
+    <t>Marian Ireneusz Szpanko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147/6 obręb: Biała Piska
+</t>
+  </si>
+  <si>
+    <t>Plac Adama Mickiewicza 16/1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL1P/00019190/8
+</t>
+  </si>
+  <si>
+    <t>małż. Andrzej Janik i 
+        Elżbieta Krystyna Janik</t>
+  </si>
+  <si>
+    <t>Plac Adama Mickiewicza 16/4</t>
+  </si>
+  <si>
+    <t>Justyna Nawrocka</t>
+  </si>
+  <si>
+    <t>Ogrodowa 1/2</t>
+  </si>
+  <si>
+    <t>Zbigniew Sebastian Nawrocki</t>
+  </si>
+  <si>
+    <t>Morelowa 1</t>
+  </si>
+  <si>
+    <t>80-180 Kowale</t>
+  </si>
+  <si>
+    <t>Emilia Kopacz</t>
+  </si>
+  <si>
+    <t>Zakład Energetyki Cieplnej Spółka Z Ograniczoną Odpowiedzialnością</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147/8 obręb: Biała Piska
+</t>
+  </si>
+  <si>
+    <t>Targowa 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL1P/00039283/3
+</t>
+  </si>
+  <si>
+    <t>Generalna Dyrekcja Dróg Krajowych I Autostrad Oddział W Olsztynie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151 obręb: Biała Piska
+</t>
+  </si>
+  <si>
+    <t>10-083 Olsztyn Ul.warszawska 89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OL1P/00028369/0
+</t>
+  </si>
+  <si>
+    <t>Skarb Państwa</t>
+  </si>
+  <si>
+    <t>111/23</t>
   </si>
 </sst>
 </file>
@@ -373,14 +542,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="13.28515625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="30.0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="23.65234375" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="17.79296875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="27.5546875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="27.6953125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="18.0" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="17.61328125" customWidth="true" bestFit="true"/>
   </cols>
@@ -410,7 +579,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="3">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s" s="4">
         <v>7</v>
@@ -436,16 +605,16 @@
         <v>13</v>
       </c>
       <c r="C3" t="s" s="4">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s" s="4">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s" s="4">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s" s="4">
         <v>12</v>
@@ -453,19 +622,19 @@
     </row>
     <row r="4">
       <c r="B4" t="s" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s" s="4">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s" s="4">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s" s="4">
         <v>16</v>
       </c>
-      <c r="D4" t="s" s="4">
+      <c r="F4" t="s" s="4">
         <v>17</v>
-      </c>
-      <c r="E4" t="s" s="4">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s" s="4">
-        <v>18</v>
       </c>
       <c r="G4" t="s" s="4">
         <v>12</v>
@@ -473,19 +642,19 @@
     </row>
     <row r="5">
       <c r="B5" t="s" s="4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s" s="4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s" s="4">
         <v>10</v>
       </c>
       <c r="F5" t="s" s="4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s" s="4">
         <v>12</v>
@@ -493,19 +662,19 @@
     </row>
     <row r="6">
       <c r="B6" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s" s="4">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s" s="4">
         <v>23</v>
-      </c>
-      <c r="C6" t="s" s="4">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s" s="4">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s" s="4">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s" s="4">
-        <v>22</v>
       </c>
       <c r="G6" t="s" s="4">
         <v>12</v>
@@ -513,19 +682,19 @@
     </row>
     <row r="7">
       <c r="B7" t="s" s="4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s" s="4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s" s="4">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s" s="4">
         <v>12</v>
@@ -533,19 +702,19 @@
     </row>
     <row r="8">
       <c r="B8" t="s" s="4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s" s="4">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s" s="4">
         <v>31</v>
       </c>
       <c r="E8" t="s" s="4">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s" s="4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G8" t="s" s="4">
         <v>12</v>
@@ -576,16 +745,16 @@
         <v>37</v>
       </c>
       <c r="C10" t="s" s="4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s" s="4">
         <v>10</v>
       </c>
       <c r="F10" t="s" s="4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s" s="4">
         <v>12</v>
@@ -593,19 +762,19 @@
     </row>
     <row r="11">
       <c r="B11" t="s" s="4">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s" s="4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s" s="4">
         <v>10</v>
       </c>
       <c r="F11" t="s" s="4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G11" t="s" s="4">
         <v>12</v>
@@ -616,16 +785,16 @@
         <v>43</v>
       </c>
       <c r="C12" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s" s="4">
         <v>44</v>
       </c>
-      <c r="D12" t="s" s="4">
-        <v>45</v>
-      </c>
       <c r="E12" t="s" s="4">
         <v>10</v>
       </c>
       <c r="F12" t="s" s="4">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G12" t="s" s="4">
         <v>12</v>
@@ -633,19 +802,19 @@
     </row>
     <row r="13">
       <c r="B13" t="s" s="4">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s" s="4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s" s="4">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s" s="4">
         <v>10</v>
       </c>
       <c r="F13" t="s" s="4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G13" t="s" s="4">
         <v>12</v>
@@ -653,19 +822,19 @@
     </row>
     <row r="14">
       <c r="B14" t="s" s="4">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s" s="4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s" s="4">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E14" t="s" s="4">
         <v>10</v>
       </c>
       <c r="F14" t="s" s="4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G14" t="s" s="4">
         <v>12</v>
@@ -673,19 +842,19 @@
     </row>
     <row r="15">
       <c r="B15" t="s" s="4">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s" s="4">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s" s="4">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E15" t="s" s="4">
         <v>10</v>
       </c>
       <c r="F15" t="s" s="4">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G15" t="s" s="4">
         <v>12</v>
@@ -693,19 +862,19 @@
     </row>
     <row r="16">
       <c r="B16" t="s" s="4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s" s="4">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s" s="4">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E16" t="s" s="4">
         <v>10</v>
       </c>
       <c r="F16" t="s" s="4">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G16" t="s" s="4">
         <v>12</v>
@@ -713,19 +882,19 @@
     </row>
     <row r="17">
       <c r="B17" t="s" s="4">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s" s="4">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s" s="4">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E17" t="s" s="4">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s" s="4">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G17" t="s" s="4">
         <v>12</v>
@@ -733,19 +902,19 @@
     </row>
     <row r="18">
       <c r="B18" t="s" s="4">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s" s="4">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s" s="4">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E18" t="s" s="4">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="F18" t="s" s="4">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="G18" t="s" s="4">
         <v>12</v>
@@ -753,19 +922,19 @@
     </row>
     <row r="19">
       <c r="B19" t="s" s="4">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s" s="4">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s" s="4">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s" s="4">
         <v>10</v>
       </c>
       <c r="F19" t="s" s="4">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="G19" t="s" s="4">
         <v>12</v>
@@ -773,19 +942,19 @@
     </row>
     <row r="20">
       <c r="B20" t="s" s="4">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s" s="4">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s" s="4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E20" t="s" s="4">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s" s="4">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="G20" t="s" s="4">
         <v>12</v>
@@ -793,28 +962,562 @@
     </row>
     <row r="21">
       <c r="B21" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="D21" t="s" s="4">
+        <v>62</v>
+      </c>
+      <c r="E21" t="s" s="4">
+        <v>56</v>
+      </c>
+      <c r="F21" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="G21" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="s" s="4">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="D22" t="s" s="4">
+        <v>64</v>
+      </c>
+      <c r="E22" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="G22" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="s" s="4">
+        <v>65</v>
+      </c>
+      <c r="C23" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="D23" t="s" s="4">
+        <v>66</v>
+      </c>
+      <c r="E23" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="G23" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="s" s="4">
+        <v>67</v>
+      </c>
+      <c r="C24" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="D24" t="s" s="4">
+        <v>68</v>
+      </c>
+      <c r="E24" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="G24" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="s" s="4">
+        <v>69</v>
+      </c>
+      <c r="C25" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="D25" t="s" s="4">
+        <v>70</v>
+      </c>
+      <c r="E25" t="s" s="4">
+        <v>71</v>
+      </c>
+      <c r="F25" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="G25" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="s" s="4">
+        <v>72</v>
+      </c>
+      <c r="C26" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="D26" t="s" s="4">
         <v>73</v>
       </c>
-      <c r="C21" t="s" s="4">
-        <v>69</v>
-      </c>
-      <c r="D21" t="s" s="4">
+      <c r="E26" t="s" s="4">
+        <v>56</v>
+      </c>
+      <c r="F26" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="G26" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="s" s="4">
         <v>74</v>
       </c>
-      <c r="E21" t="s" s="4">
+      <c r="C27" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="D27" t="s" s="4">
         <v>75</v>
       </c>
-      <c r="F21" t="s" s="4">
-        <v>72</v>
-      </c>
-      <c r="G21" t="s" s="4">
+      <c r="E27" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="G27" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="s" s="4">
+        <v>76</v>
+      </c>
+      <c r="C28" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="D28" t="s" s="4">
+        <v>77</v>
+      </c>
+      <c r="E28" t="s" s="4">
+        <v>78</v>
+      </c>
+      <c r="F28" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="G28" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="s" s="4">
+        <v>79</v>
+      </c>
+      <c r="C29" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="D29" t="s" s="4">
+        <v>80</v>
+      </c>
+      <c r="E29" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="G29" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="C30" t="s" s="4">
+        <v>82</v>
+      </c>
+      <c r="D30" t="s" s="4">
+        <v>83</v>
+      </c>
+      <c r="E30" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s" s="4">
+        <v>84</v>
+      </c>
+      <c r="G30" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="s" s="4">
+        <v>85</v>
+      </c>
+      <c r="C31" t="s" s="4">
+        <v>82</v>
+      </c>
+      <c r="D31" t="s" s="4">
+        <v>86</v>
+      </c>
+      <c r="E31" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s" s="4">
+        <v>84</v>
+      </c>
+      <c r="G31" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="s" s="4">
+        <v>87</v>
+      </c>
+      <c r="C32" t="s" s="4">
+        <v>82</v>
+      </c>
+      <c r="D32" t="s" s="4">
+        <v>88</v>
+      </c>
+      <c r="E32" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s" s="4">
+        <v>84</v>
+      </c>
+      <c r="G32" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="s" s="4">
+        <v>89</v>
+      </c>
+      <c r="C33" t="s" s="4">
+        <v>90</v>
+      </c>
+      <c r="D33" t="s" s="4">
+        <v>91</v>
+      </c>
+      <c r="E33" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="G33" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="s" s="4">
+        <v>93</v>
+      </c>
+      <c r="C34" t="s" s="4">
+        <v>90</v>
+      </c>
+      <c r="D34" t="s" s="4">
+        <v>94</v>
+      </c>
+      <c r="E34" t="s" s="4">
+        <v>95</v>
+      </c>
+      <c r="F34" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="G34" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="s" s="4">
+        <v>96</v>
+      </c>
+      <c r="C35" t="s" s="4">
+        <v>90</v>
+      </c>
+      <c r="D35" t="s" s="4">
+        <v>97</v>
+      </c>
+      <c r="E35" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F35" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="G35" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="s" s="4">
+        <v>98</v>
+      </c>
+      <c r="C36" t="s" s="4">
+        <v>90</v>
+      </c>
+      <c r="D36" t="s" s="4">
+        <v>99</v>
+      </c>
+      <c r="E36" t="s" s="4">
+        <v>56</v>
+      </c>
+      <c r="F36" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="G36" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="s" s="4">
+        <v>100</v>
+      </c>
+      <c r="C37" t="s" s="4">
+        <v>90</v>
+      </c>
+      <c r="D37" t="s" s="4">
+        <v>101</v>
+      </c>
+      <c r="E37" t="s" s="4">
+        <v>102</v>
+      </c>
+      <c r="F37" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="G37" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="s" s="4">
+        <v>103</v>
+      </c>
+      <c r="C38" t="s" s="4">
+        <v>90</v>
+      </c>
+      <c r="D38" t="s" s="4">
+        <v>104</v>
+      </c>
+      <c r="E38" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F38" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="G38" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="s" s="4">
+        <v>105</v>
+      </c>
+      <c r="C39" t="s" s="4">
+        <v>90</v>
+      </c>
+      <c r="D39" t="s" s="4">
+        <v>106</v>
+      </c>
+      <c r="E39" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="G39" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="s" s="4">
+        <v>107</v>
+      </c>
+      <c r="C40" t="s" s="4">
+        <v>90</v>
+      </c>
+      <c r="D40" t="s" s="4">
+        <v>108</v>
+      </c>
+      <c r="E40" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F40" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="G40" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="s" s="4">
+        <v>109</v>
+      </c>
+      <c r="C41" t="s" s="4">
+        <v>110</v>
+      </c>
+      <c r="D41" t="s" s="4">
+        <v>111</v>
+      </c>
+      <c r="E41" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s" s="4">
+        <v>112</v>
+      </c>
+      <c r="G41" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="s" s="4">
+        <v>113</v>
+      </c>
+      <c r="C42" t="s" s="4">
+        <v>110</v>
+      </c>
+      <c r="D42" t="s" s="4">
+        <v>114</v>
+      </c>
+      <c r="E42" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F42" t="s" s="4">
+        <v>112</v>
+      </c>
+      <c r="G42" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="s" s="4">
+        <v>115</v>
+      </c>
+      <c r="C43" t="s" s="4">
+        <v>110</v>
+      </c>
+      <c r="D43" t="s" s="4">
+        <v>116</v>
+      </c>
+      <c r="E43" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F43" t="s" s="4">
+        <v>112</v>
+      </c>
+      <c r="G43" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="s" s="4">
+        <v>117</v>
+      </c>
+      <c r="C44" t="s" s="4">
+        <v>110</v>
+      </c>
+      <c r="D44" t="s" s="4">
+        <v>118</v>
+      </c>
+      <c r="E44" t="s" s="4">
+        <v>119</v>
+      </c>
+      <c r="F44" t="s" s="4">
+        <v>112</v>
+      </c>
+      <c r="G44" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="s" s="4">
+        <v>120</v>
+      </c>
+      <c r="C45" t="s" s="4">
+        <v>110</v>
+      </c>
+      <c r="D45" t="s" s="4">
+        <v>116</v>
+      </c>
+      <c r="E45" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F45" t="s" s="4">
+        <v>112</v>
+      </c>
+      <c r="G45" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="s" s="4">
+        <v>121</v>
+      </c>
+      <c r="C46" t="s" s="4">
+        <v>122</v>
+      </c>
+      <c r="D46" t="s" s="4">
+        <v>123</v>
+      </c>
+      <c r="E46" t="s" s="4">
+        <v>10</v>
+      </c>
+      <c r="F46" t="s" s="4">
+        <v>124</v>
+      </c>
+      <c r="G46" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="s" s="4">
+        <v>125</v>
+      </c>
+      <c r="C47" t="s" s="4">
+        <v>126</v>
+      </c>
+      <c r="D47" t="s" s="4">
+        <v>127</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" t="s" s="4">
+        <v>128</v>
+      </c>
+      <c r="G47" t="s" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="s" s="4">
+        <v>129</v>
+      </c>
+      <c r="C48" t="s" s="4">
+        <v>126</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" t="s" s="4">
+        <v>128</v>
+      </c>
+      <c r="G48" t="s" s="4">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" sqref="A2" allowBlank="true" errorStyle="stop">
-      <formula1>"161,162/1,162/12,162/14,162/16,162/18,162/19,162/20,162/21,162/3,162/5,162/7,162/9,164,50/2"</formula1>
+      <formula1>"111/23,113,147/1,147/10,147/12,147/13,147/16,147/17,147/19,147/21,147/22,147/4,147/6,147/8,148/1,148/2,151,157"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
